--- a/FreshGuard_WBS.xlsx
+++ b/FreshGuard_WBS.xlsx
@@ -678,9 +678,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -690,6 +687,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,72 +993,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28" x14ac:dyDescent="0.8">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="28" x14ac:dyDescent="0.8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-    </row>
-    <row r="4" spans="1:12" s="19" customFormat="1" ht="35" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="4" spans="1:12" s="18" customFormat="1" ht="35" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="20" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1243,216 +1243,230 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
         <v>3</v>
       </c>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
         <v>1.5</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
         <v>2</v>
       </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="G11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
         <v>4</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>2</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="1" t="s">
+      <c r="G12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>1.7</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="1" t="s">
+      <c r="G15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16" s="6">
         <v>1.9</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
         <v>3</v>
       </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="6">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="G16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
@@ -1491,36 +1505,38 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>1.1100000000000001</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="G18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
@@ -1963,34 +1979,36 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4">
         <v>4</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="4">
         <v>3.2</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="1" t="s">
+      <c r="G33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5">
+        <v>1</v>
+      </c>
+      <c r="L33" s="4"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
@@ -2683,36 +2701,38 @@
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>6.6</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2">
         <v>6.5</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H55" s="1" t="s">
+      <c r="G55" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
+      <c r="J55" s="3">
+        <v>1</v>
+      </c>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="61" spans="1:12" ht="22" x14ac:dyDescent="0.65">
       <c r="A61" s="10" t="s">
